--- a/prova_real/trimestre_10/resultado_T10.xlsx
+++ b/prova_real/trimestre_10/resultado_T10.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -598,10 +598,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.26</v>
+        <v>13.4</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>38.52</v>
+        <v>34.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>8.74</v>
+        <v>10.02</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-0.0926</v>
+        <v>-0.5376</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1834.29</v>
+        <v>1927.78</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>6596.19</v>
+        <v>7483.33</v>
       </c>
     </row>
     <row r="3">
@@ -655,12 +655,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.86</v>
+        <v>7.66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>26.43</v>
+        <v>29.45</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>9.31</v>
+        <v>10.36</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-0.9268</v>
+        <v>-1.3172</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1258.57</v>
+        <v>1636.11</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>6020.48</v>
+        <v>7191.67</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.7</v>
+        <v>62.9</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.98</v>
+        <v>11.44</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23.7</v>
+        <v>26.26</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>9.68</v>
+        <v>15.92</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-1.8061</v>
+        <v>-5.7513</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1128.57</v>
+        <v>1458.89</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5890.48</v>
+        <v>7014.44</v>
       </c>
     </row>
     <row r="5">
@@ -798,32 +798,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11.14</v>
+        <v>22.97</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>23.53</v>
+        <v>24.74</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3.99</v>
+        <v>0.49</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-7.0666</v>
+        <v>-1.6198</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1120.48</v>
+        <v>1374.44</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>5882.38</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="6">
@@ -872,32 +872,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.64</v>
+        <v>13.18</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22.99</v>
+        <v>23.03</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.63</v>
+        <v>7.63</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-0.0951</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1094.76</v>
+        <v>1279.44</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5856.67</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="7">
@@ -946,17 +946,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -968,10 +968,10 @@
         <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>13.71</v>
+        <v>17.13</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>22.04</v>
+        <v>21.38</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>11.17</v>
+        <v>3.93</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-1.4524</v>
+        <v>0.588</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1049.52</v>
+        <v>1187.78</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>5811.43</v>
+        <v>6743.33</v>
       </c>
     </row>
     <row r="8">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1042,10 +1042,10 @@
         <v>58.1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17.46</v>
+        <v>6.19</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.24</v>
+        <v>20.42</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.14</v>
+        <v>0.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.32</v>
+        <v>7.36</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4959</v>
+        <v>-1.6241</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>963.8099999999999</v>
+        <v>1134.44</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>5725.71</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="9">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>19.48</v>
+        <v>19.88</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.58</v>
+        <v>2.87</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.0376</v>
+        <v>0.5284</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>927.62</v>
+        <v>1104.44</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>5689.52</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="10">
@@ -1168,32 +1168,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>14.33</v>
+        <v>5.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17.74</v>
+        <v>19.68</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.78</v>
+        <v>3.11</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>9.92</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-0.582</v>
+        <v>-2.2824</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>844.76</v>
+        <v>1093.33</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>5606.67</v>
+        <v>6648.89</v>
       </c>
     </row>
     <row r="11">
@@ -1242,32 +1242,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6.48</v>
+        <v>13.31</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>17.45</v>
+        <v>18.69</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1.57</v>
+        <v>0.71</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>6.46</v>
+        <v>3.83</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-1.8202</v>
+        <v>0.098</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>830.95</v>
+        <v>1038.33</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>5592.86</v>
+        <v>6593.89</v>
       </c>
     </row>
     <row r="12">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1338,10 +1338,10 @@
         <v>58.1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.04</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.15</v>
+        <v>18.48</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.37</v>
+        <v>1.39</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.05</v>
+        <v>10.13</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-0.8088</v>
+        <v>-2.3595</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>816.67</v>
+        <v>1026.67</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>5578.57</v>
+        <v>6582.22</v>
       </c>
     </row>
     <row r="13">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1412,10 +1412,10 @@
         <v>61.3</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>15.93</v>
+        <v>17.93</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-2.0488</v>
+        <v>-2.2084</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>758.5700000000001</v>
+        <v>996.11</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>5520.48</v>
+        <v>6551.67</v>
       </c>
     </row>
     <row r="14">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.92</v>
+        <v>5.77</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.81</v>
+        <v>14.28</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.08</v>
+        <v>3.43</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.12</v>
+        <v>12.7</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.1837</v>
+        <v>-10.2454</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>752.86</v>
+        <v>793.33</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>5514.76</v>
+        <v>6348.89</v>
       </c>
     </row>
     <row r="15">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BEES3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.42</v>
+        <v>6.4</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>15.79</v>
+        <v>14.26</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.22</v>
+        <v>1.65</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.19</v>
+        <v>6.78</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5048</v>
+        <v>-2.4874</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>751.9</v>
+        <v>792.22</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>5513.81</v>
+        <v>6347.78</v>
       </c>
     </row>
     <row r="16">
@@ -1612,32 +1612,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>BEES3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.29</v>
+        <v>6.38</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.29</v>
+        <v>13.37</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.17</v>
+        <v>3.08</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>-0.2413</v>
+        <v>0.4857</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>728.1</v>
+        <v>742.78</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>5490</v>
+        <v>6298.33</v>
       </c>
     </row>
     <row r="17">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>59.7</v>
+        <v>54.8</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6.36</v>
+        <v>9.25</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15.08</v>
+        <v>10.82</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>8.59</v>
+        <v>3.73</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-1.0281</v>
+        <v>-0.4805</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>718.1</v>
+        <v>601.11</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>5480</v>
+        <v>6156.67</v>
       </c>
     </row>
     <row r="18">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1782,10 +1782,10 @@
         <v>56.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7.54</v>
+        <v>2.23</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1808,22 +1808,22 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>9.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-15.9029</v>
+        <v>-4.2933</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>359.05</v>
+        <v>123.89</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>5120.95</v>
+        <v>5679.44</v>
       </c>
     </row>
     <row r="19">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1856,10 +1856,10 @@
         <v>56.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2.27</v>
+        <v>-3.69</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1882,244 +1882,244 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2.4</v>
+        <v>0.38</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>9.57</v>
+        <v>11.53</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-4.3073</v>
+        <v>-17.1126</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>108.1</v>
+        <v>-205</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>4870</v>
+        <v>5350.56</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>GGPS3</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>-1.797</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>4822.38</v>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>JSLG3</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-4.4736</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>CPFE3</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>-1.0795</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>4651.9</v>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>DIRR3</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-0.7351</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>KLBN4</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>-16.279</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>-191.43</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>4570.48</v>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>RECV3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2130,17 +2130,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2152,10 +2152,10 @@
         <v>53.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.66</v>
+        <v>12.55</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>24.56</v>
+        <v>20.71</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>17.28</v>
+        <v>8.49</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-3.0531</v>
+        <v>-0.9105</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0</v>
@@ -2204,17 +2204,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2226,10 +2226,10 @@
         <v>53.2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>23.93</v>
+        <v>6.66</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>19.79</v>
+        <v>14.39</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>0.54</v>
+        <v>0.09</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>16.61</v>
+        <v>3.43</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>-2.3145</v>
+        <v>0.1286</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0</v>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2300,10 +2300,10 @@
         <v>53.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.22</v>
+        <v>15.46</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.64</v>
+        <v>13.95</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0.34</v>
+        <v>0.85</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>2.51</v>
+        <v>11.42</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0.6718</v>
+        <v>-4.495</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2374,10 +2374,10 @@
         <v>53.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5.68</v>
+        <v>4.82</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>14.64</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>3.66</v>
+        <v>4.74</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-0.0919</v>
+        <v>-1.3184</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>MELK3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2448,10 +2448,10 @@
         <v>53.2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.58</v>
+        <v>10</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>11.56</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.97</v>
+        <v>6.64</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.5748</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2522,10 +2522,10 @@
         <v>53.2</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>11.35</v>
+        <v>10.93</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>6.92</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4.8</v>
+        <v>1.07</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>9.67</v>
+        <v>7.72</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>-13.1808</v>
+        <v>-2.9348</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -2574,17 +2574,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2596,10 +2596,10 @@
         <v>53.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10.37</v>
+        <v>14.91</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.81</v>
+        <v>7.52</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>6.55</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.3123</v>
+        <v>-1.7328</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2648,17 +2648,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2670,10 +2670,10 @@
         <v>53.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.880000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>5.6</v>
+        <v>6.18</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.2</v>
+        <v>1.15</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>2.46</v>
+        <v>12.86</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-0.9295</v>
+        <v>-8.254899999999999</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2744,10 +2744,10 @@
         <v>53.2</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>15.57</v>
+        <v>6.91</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5.06</v>
+        <v>5.38</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.7141</v>
+        <v>-10.9568</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0</v>
@@ -2796,17 +2796,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2818,10 +2818,10 @@
         <v>53.2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>7.81</v>
+        <v>8.24</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4.47</v>
+        <v>1.86</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>4.52</v>
+        <v>0.57</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>16.8</v>
+        <v>3.63</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>-15.7636</v>
+        <v>-1.5938</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>SAPR3</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2892,10 +2892,10 @@
         <v>53.2</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.91</v>
+        <v>9.58</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-3.88</v>
+        <v>1.66</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
@@ -2904,257 +2904,257 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>-4.7063</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>YDUQ3</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>-10.8435</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>CPFE3</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>⚠️ OBSERVAR</t>
         </is>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>-14.5389</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>BMGB4</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>-2.1567</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>ITUB3</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>-9.2164</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="4" t="n">
+      <c r="M35" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>-1.0874</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>ITUB4</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>KLBN11</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="3" t="n">
         <v>53.2</v>
       </c>
-      <c r="G36" s="4" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>-10.9351</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="4" t="n">
+      <c r="G36" s="3" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>-15.9509</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3166,17 +3166,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ODPV3</t>
+          <t>BMGB4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3185,13 +3185,13 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>14.43</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>5.74</v>
+        <v>25.38</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>-0.8747</v>
+        <v>-2.6532</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SAUD3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>14.43</v>
+        <v>19.34</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.58</v>
+        <v>0.1</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>5.74</v>
+        <v>5.07</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.8747</v>
+        <v>-0.9709</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,17 +3314,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3336,10 +3336,10 @@
         <v>54.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>14.41</v>
+        <v>18.66</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.8</v>
+        <v>2.62</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>10.82</v>
+        <v>13.16</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-9.5375</v>
+        <v>-9.3489</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,36 +3388,36 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-235.59</v>
+        <v>3.29</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>12.37</v>
+        <v>16.12</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>4.6</v>
+        <v>3.09</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>112.73</v>
+        <v>12.96</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>-277.2858</v>
+        <v>-10.6909</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>EMBJ3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3484,14 +3484,14 @@
         <v>53.2</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.36</v>
+        <v>-0.67</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>7.29</v>
+        <v>13.52</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.97</v>
+        <v>4.16</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>2.83</v>
+        <v>18.67</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>0.0186</v>
+        <v>-19.3971</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,32 +3536,32 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1.53</v>
+        <v>2.83</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>6.78</v>
+        <v>12.97</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>5.15</v>
+        <v>11</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-1.4158</v>
+        <v>-10.2596</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>54.8</v>
+        <v>62.9</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>6.06</v>
+        <v>11.76</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>4.44</v>
+        <v>6.89</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.1</v>
+        <v>-1.4271</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3684,36 +3684,36 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>ASAI3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>2.64</v>
+        <v>-1.11</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>2.77</v>
+        <v>7.43</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>7.07</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>-6.7267</v>
+        <v>-4.2824</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -3758,17 +3758,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3780,14 +3780,14 @@
         <v>53.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-19.88</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.63</v>
+        <v>6.93</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>3.31</v>
+        <v>1.26</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>25.23</v>
+        <v>4.83</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>-19.0015</v>
+        <v>-1.0348</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -3832,41 +3832,41 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-17.89</v>
+        <v>2.49</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-1.46</v>
+        <v>4.36</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>1.96</v>
+        <v>0.97</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>18.76</v>
+        <v>6.67</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>-45.2942</v>
+        <v>-5.5417</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -3906,32 +3906,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-8.289999999999999</v>
+        <v>-65.61</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-3.62</v>
+        <v>3.96</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>0.99</v>
+        <v>9</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>3.28</v>
+        <v>49</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>0.3538</v>
+        <v>-80.43810000000001</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4002,10 +4002,10 @@
         <v>54.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-12.73</v>
+        <v>-14.54</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-4.35</v>
+        <v>3.06</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>1.07</v>
+        <v>1.37</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>5.58</v>
+        <v>7.04</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.0057</v>
+        <v>-0.4965</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
@@ -4054,41 +4054,41 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>2.15</v>
+        <v>-18.4</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-4.39</v>
+        <v>0.65</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.43</v>
+        <v>2.05</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>7.04</v>
+        <v>19.63</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-1.3793</v>
+        <v>-49.4051</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>0</v>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -4150,10 +4150,10 @@
         <v>53.2</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-21.94</v>
+        <v>-23.08</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-4.72</v>
+        <v>-1.79</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>5.48</v>
+        <v>5.05</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>-2.6525</v>
+        <v>-1.8826</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -4202,32 +4202,32 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-2</v>
+        <v>-9.52</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-4.82</v>
+        <v>-2.73</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>2.69</v>
+        <v>1.06</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>10.65</v>
+        <v>3.43</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>-12.7888</v>
+        <v>0.23</v>
       </c>
       <c r="P51" s="4" t="n">
         <v>0</v>
@@ -4276,32 +4276,32 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CBAV3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-17.16</v>
+        <v>-7.72</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-5.39</v>
+        <v>-3.63</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>15.41</v>
+        <v>8.25</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>-2.7389</v>
+        <v>-5.4299</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-63.34</v>
+        <v>-300.6</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>-8.09</v>
+        <v>-4.63</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>8.58</v>
+        <v>5.36</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>46.87</v>
+        <v>132.5</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>-75.7491</v>
+        <v>-354.1611</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0</v>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.74</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-9.48</v>
+        <v>-5.85</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>5.42</v>
+        <v>5.33</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-0.0772</v>
+        <v>-0.0406</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
@@ -4498,32 +4498,32 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-5.83</v>
+        <v>-1.65</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>-10.76</v>
+        <v>-7.03</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>6.81</v>
+        <v>10.97</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>-0.7212</v>
+        <v>-10.7817</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0</v>
@@ -4572,32 +4572,32 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-22.12</v>
+        <v>-0.4</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-12.37</v>
+        <v>-7.62</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>14.51</v>
+        <v>3.88</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>-3.3898</v>
+        <v>-0.3607</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
@@ -4646,32 +4646,32 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-2.65</v>
+        <v>-1.32</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>-15.93</v>
+        <v>-7.69</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>2.19</v>
+        <v>0.21</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>16.32</v>
+        <v>3.01</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>-3.6891</v>
+        <v>-0.0859</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -4720,32 +4720,32 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>59.7</v>
+        <v>53.2</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.92</v>
+        <v>-2.68</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-18.15</v>
+        <v>-8.82</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>7.27</v>
+        <v>5.35</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>-1.2162</v>
+        <v>-1.0703</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>0</v>
@@ -4794,17 +4794,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>NGRD3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4816,10 +4816,10 @@
         <v>53.2</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-11.86</v>
+        <v>-0.44</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>-18.18</v>
+        <v>-9.9</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>0.66</v>
+        <v>0.12</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2.32</v>
+        <v>4.45</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0.728</v>
+        <v>-0.138</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0</v>
@@ -4868,32 +4868,32 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-6.65</v>
+        <v>-16.72</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-22.81</v>
+        <v>-10.83</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>2.67</v>
+        <v>0.66</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>6.3</v>
+        <v>14.82</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.3207</v>
+        <v>-2.3735</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -4942,17 +4942,17 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>BLAU3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-14.91</v>
+        <v>-6.5</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>-22.98</v>
+        <v>-13.61</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.68</v>
+        <v>3.8</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>7.2</v>
+        <v>6.88</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>0.5683</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>0</v>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>62.9</v>
+        <v>56.5</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-57.33</v>
+        <v>-0.67</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-23.84</v>
+        <v>-15.96</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5064,13 +5064,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>2.29</v>
+        <v>0.73</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>32.48</v>
+        <v>8.48</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>-14.9852</v>
+        <v>-1.7394</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -5090,32 +5090,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>NGRD3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-27.3</v>
+        <v>-13.19</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>-25.49</v>
+        <v>-17.69</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>11.47</v>
+        <v>2.26</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>0.1152</v>
+        <v>0.8024</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
@@ -5164,32 +5164,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>ESPA3</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-4.01</v>
+        <v>-2.48</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-30</v>
+        <v>-17.72</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.22</v>
+        <v>2.01</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>21.46</v>
+        <v>14.9</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>-3.2095</v>
+        <v>-2.66</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -5238,32 +5238,32 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>AMAR3</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-11.68</v>
+        <v>-30.24</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>-37.47</v>
+        <v>-20.07</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>11.06</v>
+        <v>12.83</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -5312,32 +5312,32 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-142.23</v>
+        <v>-7.21</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>-42.03</v>
+        <v>-23.06</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5360,13 +5360,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>6.81</v>
+        <v>2.43</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>73.42</v>
+        <v>5.82</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>-10.7246</v>
+        <v>0.3627</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>0</v>
@@ -5386,17 +5386,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>FHER3</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -5408,10 +5408,10 @@
         <v>62.9</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-39.13</v>
+        <v>-61.42</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>-57.11</v>
+        <v>-23.58</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
@@ -5434,13 +5434,13 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>6.44</v>
+        <v>2.53</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>13.43</v>
+        <v>36.39</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>0.5825</v>
+        <v>-14.5024</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>0</v>
@@ -5460,69 +5460,439 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
+          <t>BLAU3</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-14.99</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>-23.96</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>ESPA3</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>-28.26</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>-3.2747</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>AMAR3</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>-38.21</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-166.82</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>-42.48</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>-18.5505</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>AGXY3</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>-38.19</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>-59.38</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>PDGR3</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>-39.61</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>-87.97</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="F73" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>-87.79000000000001</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M68" s="4" t="n">
-        <v>44735.38</v>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>408.55</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>-4.9179</v>
-      </c>
-      <c r="P68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" s="4" t="n">
+      <c r="M73" s="4" t="n">
+        <v>39639.45</v>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>-5.406</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5537,7 +5907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5665,12 +6035,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5682,10 +6052,10 @@
         <v>56.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14.26</v>
+        <v>13.4</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>38.52</v>
+        <v>34.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -5708,22 +6078,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>8.74</v>
+        <v>10.02</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-0.0926</v>
+        <v>-0.5376</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1834.29</v>
+        <v>1927.78</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>6596.19</v>
+        <v>7483.33</v>
       </c>
     </row>
     <row r="3">
@@ -5739,12 +6109,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5753,13 +6123,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7.86</v>
+        <v>7.66</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>26.43</v>
+        <v>29.45</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -5782,22 +6152,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>9.31</v>
+        <v>10.36</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-0.9268</v>
+        <v>-1.3172</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1258.57</v>
+        <v>1636.11</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>6020.48</v>
+        <v>7191.67</v>
       </c>
     </row>
     <row r="4">
@@ -5808,17 +6178,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5827,13 +6197,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.7</v>
+        <v>62.9</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9.98</v>
+        <v>11.44</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23.7</v>
+        <v>26.26</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -5856,22 +6226,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>9.68</v>
+        <v>15.92</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-1.8061</v>
+        <v>-5.7513</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1128.57</v>
+        <v>1458.89</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5890.48</v>
+        <v>7014.44</v>
       </c>
     </row>
     <row r="5">
@@ -5882,32 +6252,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11.14</v>
+        <v>22.97</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>23.53</v>
+        <v>24.74</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -5930,22 +6300,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3.99</v>
+        <v>0.49</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-7.0666</v>
+        <v>-1.6198</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1120.48</v>
+        <v>1374.44</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>5882.38</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="6">
@@ -5956,32 +6326,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5.64</v>
+        <v>13.18</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>22.99</v>
+        <v>23.03</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -6004,22 +6374,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.63</v>
+        <v>7.63</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-0.0951</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1094.76</v>
+        <v>1279.44</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>5856.67</v>
+        <v>6835</v>
       </c>
     </row>
     <row r="7">
@@ -6030,17 +6400,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6052,10 +6422,10 @@
         <v>56.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>13.71</v>
+        <v>17.13</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>22.04</v>
+        <v>21.38</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -6078,22 +6448,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>11.17</v>
+        <v>3.93</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-1.4524</v>
+        <v>0.588</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1049.52</v>
+        <v>1187.78</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>5811.43</v>
+        <v>6743.33</v>
       </c>
     </row>
     <row r="8">
@@ -6104,17 +6474,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6126,10 +6496,10 @@
         <v>58.1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17.46</v>
+        <v>6.19</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>20.24</v>
+        <v>20.42</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -6152,22 +6522,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.14</v>
+        <v>0.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.32</v>
+        <v>7.36</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4959</v>
+        <v>-1.6241</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>963.8099999999999</v>
+        <v>1134.44</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>5725.71</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="9">
@@ -6178,17 +6548,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6200,10 +6570,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>19.48</v>
+        <v>19.88</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -6226,22 +6596,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.58</v>
+        <v>2.87</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.0376</v>
+        <v>0.5284</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>927.62</v>
+        <v>1104.44</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>5689.52</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="10">
@@ -6252,32 +6622,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>14.33</v>
+        <v>5.36</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17.74</v>
+        <v>19.68</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -6300,22 +6670,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.78</v>
+        <v>3.11</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>9.92</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>-0.582</v>
+        <v>-2.2824</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>844.76</v>
+        <v>1093.33</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>5606.67</v>
+        <v>6648.89</v>
       </c>
     </row>
     <row r="11">
@@ -6326,32 +6696,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6.48</v>
+        <v>13.31</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>17.45</v>
+        <v>18.69</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -6374,22 +6744,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1.57</v>
+        <v>0.71</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>6.46</v>
+        <v>3.83</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>-1.8202</v>
+        <v>0.098</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>830.95</v>
+        <v>1038.33</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>5592.86</v>
+        <v>6593.89</v>
       </c>
     </row>
     <row r="12">
@@ -6400,17 +6770,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6422,10 +6792,10 @@
         <v>58.1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7.04</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>17.15</v>
+        <v>18.48</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -6448,22 +6818,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.37</v>
+        <v>1.39</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.05</v>
+        <v>10.13</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-0.8088</v>
+        <v>-2.3595</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>816.67</v>
+        <v>1026.67</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>5578.57</v>
+        <v>6582.22</v>
       </c>
     </row>
     <row r="13">
@@ -6479,12 +6849,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6496,10 +6866,10 @@
         <v>61.3</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>15.93</v>
+        <v>17.93</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -6522,22 +6892,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-2.0488</v>
+        <v>-2.2084</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>758.5700000000001</v>
+        <v>996.11</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>5520.48</v>
+        <v>6551.67</v>
       </c>
     </row>
     <row r="14">
@@ -6548,32 +6918,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9.92</v>
+        <v>5.77</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.81</v>
+        <v>14.28</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -6596,22 +6966,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.08</v>
+        <v>3.43</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.12</v>
+        <v>12.7</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>0.1837</v>
+        <v>-10.2454</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>752.86</v>
+        <v>793.33</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>5514.76</v>
+        <v>6348.89</v>
       </c>
     </row>
     <row r="15">
@@ -6622,17 +6992,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BEES3</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6641,13 +7011,13 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7.42</v>
+        <v>6.4</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>15.79</v>
+        <v>14.26</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -6670,22 +7040,22 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.22</v>
+        <v>1.65</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.19</v>
+        <v>6.78</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5048</v>
+        <v>-2.4874</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>751.9</v>
+        <v>792.22</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>5513.81</v>
+        <v>6347.78</v>
       </c>
     </row>
     <row r="16">
@@ -6696,32 +7066,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>BEES3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.29</v>
+        <v>6.38</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>15.29</v>
+        <v>13.37</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -6744,22 +7114,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.17</v>
+        <v>3.08</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>-0.2413</v>
+        <v>0.4857</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>728.1</v>
+        <v>742.78</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>5490</v>
+        <v>6298.33</v>
       </c>
     </row>
     <row r="17">
@@ -6770,32 +7140,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>59.7</v>
+        <v>54.8</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6.36</v>
+        <v>9.25</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15.08</v>
+        <v>10.82</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -6818,22 +7188,22 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>8.59</v>
+        <v>3.73</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-1.0281</v>
+        <v>-0.4805</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>718.1</v>
+        <v>601.11</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>5480</v>
+        <v>6156.67</v>
       </c>
     </row>
     <row r="18">
@@ -6844,17 +7214,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -6866,10 +7236,10 @@
         <v>56.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7.54</v>
+        <v>2.23</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -6892,22 +7262,22 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>9.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>-15.9029</v>
+        <v>-4.2933</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>359.05</v>
+        <v>123.89</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>5120.95</v>
+        <v>5679.44</v>
       </c>
     </row>
     <row r="19">
@@ -6918,17 +7288,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -6940,10 +7310,10 @@
         <v>56.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2.27</v>
+        <v>-3.69</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -6952,12 +7322,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -6966,244 +7336,22 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2.4</v>
+        <v>0.38</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>9.57</v>
+        <v>11.53</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-4.3073</v>
+        <v>-17.1126</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>4761.9</v>
+        <v>5555.56</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>108.1</v>
+        <v>-205</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>4870</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>GGPS3</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>-1.797</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>4822.38</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>CPFE3</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>-1.0795</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>4651.9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>T-10</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>KLBN4</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-20</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Previsibilidade Moderada</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>-16.279</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>4761.9</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>-191.43</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>4570.48</v>
+        <v>5350.56</v>
       </c>
     </row>
   </sheetData>
